--- a/Genostar/CYPs/CYP2D6/CYP2D6_Allele_def_rs_excluidos.xlsx
+++ b/Genostar/CYPs/CYP2D6/CYP2D6_Allele_def_rs_excluidos.xlsx
@@ -5,23 +5,24 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ctoma\Fobos\Proyecto_Diana\TFM_GenoStaR\Genostar\CYPs\CYP2D6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\Genostar\CYPs\CYP2D6\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28005" windowHeight="9660" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19110" windowHeight="8130" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
     <sheet name="Filtrada" sheetId="2" r:id="rId2"/>
     <sheet name="SNP-alelo" sheetId="5" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="330">
   <si>
     <t>rsID</t>
   </si>
@@ -1008,6 +1009,9 @@
   </si>
   <si>
     <t>¿esta en alguna funcion de genostar?</t>
+  </si>
+  <si>
+    <t>X.6 Corresponde a rs1569024017</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1163,6 +1167,13 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7503,4 +7514,4040 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:DR152"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="111" max="111" width="25" customWidth="1"/>
+    <col min="112" max="112" width="14.85546875" customWidth="1"/>
+    <col min="117" max="117" width="19.28515625" customWidth="1"/>
+    <col min="118" max="118" width="10.5703125" customWidth="1"/>
+    <col min="119" max="120" width="10.42578125" customWidth="1"/>
+    <col min="122" max="122" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:122" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH1" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="DI1" s="2"/>
+      <c r="DJ1" s="2"/>
+      <c r="DK1" s="2"/>
+      <c r="DL1" s="2"/>
+      <c r="DM1" s="2"/>
+      <c r="DN1" s="2"/>
+      <c r="DO1" s="2"/>
+      <c r="DP1" s="2"/>
+      <c r="DQ1" s="2"/>
+      <c r="DR1" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" spans="1:122" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>4.57E-4</v>
+      </c>
+      <c r="F2">
+        <v>5.0980000000000001E-6</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2">
+        <v>6.2830000000000007E-5</v>
+      </c>
+      <c r="L2">
+        <v>5.1789999999999997E-5</v>
+      </c>
+      <c r="M2">
+        <v>8.7449999999999998E-5</v>
+      </c>
+      <c r="N2">
+        <v>1.6980000000000001E-6</v>
+      </c>
+      <c r="O2">
+        <v>4.2440000000000004E-6</v>
+      </c>
+      <c r="P2" s="20"/>
+      <c r="Q2">
+        <v>1.214E-4</v>
+      </c>
+      <c r="R2">
+        <v>7.4709999999999995E-5</v>
+      </c>
+      <c r="S2">
+        <v>1.0190000000000001E-5</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>3.4799999999999999E-5</v>
+      </c>
+      <c r="W2" s="21"/>
+      <c r="X2">
+        <v>1.087E-4</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>1.242E-2</v>
+      </c>
+      <c r="AA2">
+        <v>5.9449999999999998E-6</v>
+      </c>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>4.0840000000000002E-5</v>
+      </c>
+      <c r="AE2">
+        <v>4.7660000000000001E-5</v>
+      </c>
+      <c r="AF2">
+        <v>1.5310000000000001E-5</v>
+      </c>
+      <c r="AG2">
+        <v>8.551E-6</v>
+      </c>
+      <c r="AH2">
+        <v>2.5689999999999999E-6</v>
+      </c>
+      <c r="AI2">
+        <v>1.7099999999999999E-6</v>
+      </c>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2">
+        <v>5.9610000000000002E-6</v>
+      </c>
+      <c r="AN2">
+        <v>3.813E-4</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>2.0560000000000001E-3</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="20"/>
+      <c r="AS2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="11">
+        <v>8.4900000000000005E-7</v>
+      </c>
+      <c r="AU2">
+        <v>3.3960000000000002E-6</v>
+      </c>
+      <c r="AV2">
+        <v>3.2270000000000001E-5</v>
+      </c>
+      <c r="AW2">
+        <v>6.2830000000000007E-5</v>
+      </c>
+      <c r="AX2" s="20"/>
+      <c r="AY2">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="AZ2">
+        <v>5.1799999999999999E-5</v>
+      </c>
+      <c r="BA2">
+        <v>5.9469999999999998E-5</v>
+      </c>
+      <c r="BB2">
+        <v>3.3979999999999999E-6</v>
+      </c>
+      <c r="BC2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>9.3510000000000008E-6</v>
+      </c>
+      <c r="BE2">
+        <v>1.1070000000000001E-5</v>
+      </c>
+      <c r="BF2">
+        <v>3.065E-2</v>
+      </c>
+      <c r="BG2">
+        <v>2.41E-4</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>2.6310000000000001E-5</v>
+      </c>
+      <c r="BJ2" s="11">
+        <v>8.4880000000000003E-7</v>
+      </c>
+      <c r="BK2" s="20"/>
+      <c r="BL2">
+        <v>1.783E-5</v>
+      </c>
+      <c r="BM2">
+        <v>4.1760000000000001E-4</v>
+      </c>
+      <c r="BN2">
+        <v>1.2390000000000001E-3</v>
+      </c>
+      <c r="BO2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ2" s="20"/>
+      <c r="BR2">
+        <v>2.1209999999999999E-5</v>
+      </c>
+      <c r="BS2">
+        <v>1.505E-3</v>
+      </c>
+      <c r="BT2">
+        <v>1.4610000000000001E-3</v>
+      </c>
+      <c r="BU2" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV2" s="11">
+        <v>8.4850000000000001E-7</v>
+      </c>
+      <c r="BW2" s="20"/>
+      <c r="BX2">
+        <v>3.0339999999999999E-2</v>
+      </c>
+      <c r="BY2">
+        <v>3.1420000000000001E-5</v>
+      </c>
+      <c r="BZ2">
+        <v>9.5249999999999998E-5</v>
+      </c>
+      <c r="CA2">
+        <v>1.13E-4</v>
+      </c>
+      <c r="CB2" s="1">
+        <v>0</v>
+      </c>
+      <c r="CC2" s="15"/>
+      <c r="CD2">
+        <v>6.0590000000000004E-4</v>
+      </c>
+      <c r="CE2">
+        <v>2.039E-5</v>
+      </c>
+      <c r="CF2">
+        <v>7.7440000000000004E-5</v>
+      </c>
+      <c r="CG2">
+        <v>4.2780000000000004E-6</v>
+      </c>
+      <c r="CH2" s="11">
+        <v>8.7219999999999999E-7</v>
+      </c>
+      <c r="CI2">
+        <v>1.0289999999999999E-4</v>
+      </c>
+      <c r="CJ2">
+        <v>4.952E-5</v>
+      </c>
+      <c r="CK2">
+        <v>1.7260000000000001E-5</v>
+      </c>
+      <c r="CL2">
+        <v>1.7230000000000001E-6</v>
+      </c>
+      <c r="CM2" s="20"/>
+      <c r="CN2" s="20"/>
+      <c r="CO2">
+        <v>2.8050000000000001E-5</v>
+      </c>
+      <c r="CP2" s="1">
+        <v>0</v>
+      </c>
+      <c r="CQ2">
+        <v>1.274E-5</v>
+      </c>
+      <c r="CR2">
+        <v>1.9539999999999999E-5</v>
+      </c>
+      <c r="CS2">
+        <v>3.6980000000000002E-5</v>
+      </c>
+      <c r="CT2">
+        <v>8.8300000000000005E-5</v>
+      </c>
+      <c r="CU2" s="15"/>
+      <c r="CV2" s="1">
+        <v>0</v>
+      </c>
+      <c r="CW2" s="20"/>
+      <c r="CX2" s="20"/>
+      <c r="CY2" s="20"/>
+      <c r="CZ2" s="20"/>
+      <c r="DA2" s="15"/>
+      <c r="DB2" s="15"/>
+      <c r="DC2">
+        <v>8.4950000000000008E-6</v>
+      </c>
+      <c r="DD2" s="1">
+        <v>0</v>
+      </c>
+      <c r="DE2">
+        <v>3.7410000000000003E-5</v>
+      </c>
+      <c r="DF2">
+        <v>9.4730000000000006E-6</v>
+      </c>
+      <c r="DG2" s="20"/>
+      <c r="DH2" s="19">
+        <f>SUM(B2:DG2)</f>
+        <v>0.10102177850000001</v>
+      </c>
+      <c r="DI2" s="19">
+        <f>DH2*100</f>
+        <v>10.10217785</v>
+      </c>
+      <c r="DJ2" s="19">
+        <f>DH2+I3+J3+W3</f>
+        <v>0.98742177850000001</v>
+      </c>
+      <c r="DK2" s="19">
+        <f>DJ2*100</f>
+        <v>98.742177850000004</v>
+      </c>
+      <c r="DL2" s="19"/>
+      <c r="DM2" s="19"/>
+      <c r="DN2" s="19"/>
+      <c r="DO2" s="19"/>
+      <c r="DP2" s="19"/>
+      <c r="DQ2" s="19"/>
+      <c r="DR2" s="19"/>
+    </row>
+    <row r="3" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.17680000000000001</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.18720000000000001</v>
+      </c>
+      <c r="W3" s="7">
+        <v>0.52239999999999998</v>
+      </c>
+      <c r="BB3" s="11"/>
+    </row>
+    <row r="4" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K4" t="s">
+        <v>114</v>
+      </c>
+      <c r="L4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M4" t="s">
+        <v>116</v>
+      </c>
+      <c r="N4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>114</v>
+      </c>
+      <c r="R4" t="s">
+        <v>115</v>
+      </c>
+      <c r="S4" t="s">
+        <v>114</v>
+      </c>
+      <c r="T4" t="s">
+        <v>114</v>
+      </c>
+      <c r="U4" t="s">
+        <v>115</v>
+      </c>
+      <c r="V4" t="s">
+        <v>113</v>
+      </c>
+      <c r="W4" t="s">
+        <v>117</v>
+      </c>
+      <c r="X4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>124</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>125</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>126</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>116</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>116</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>114</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>113</v>
+      </c>
+      <c r="CV4" t="s">
+        <v>116</v>
+      </c>
+      <c r="CW4" t="s">
+        <v>114</v>
+      </c>
+      <c r="CX4" t="s">
+        <v>115</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>114</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>114</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>115</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>113</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>114</v>
+      </c>
+      <c r="DD4" t="s">
+        <v>113</v>
+      </c>
+      <c r="DE4" t="s">
+        <v>113</v>
+      </c>
+      <c r="DF4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM5">
+        <v>0.56784000000000001</v>
+      </c>
+      <c r="DR5" s="7"/>
+    </row>
+    <row r="6" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>130</v>
+      </c>
+      <c r="DH6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="DM6" s="3">
+        <v>1.3610000000000001E-2</v>
+      </c>
+      <c r="DN6" s="3"/>
+      <c r="DO6" s="3"/>
+      <c r="DP6" s="3"/>
+      <c r="DQ6" s="3"/>
+      <c r="DR6">
+        <f>DM6</f>
+        <v>1.3610000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:122" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="CO7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="CQ7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="CR7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="CS7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="CU7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="CV7" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="CX7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="CY7" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="CZ7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="DA7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="DB7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="DC7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="DD7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="DH7" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="DI7" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="DR7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="DG8" t="s">
+        <v>136</v>
+      </c>
+      <c r="DH8" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="DR8" s="12"/>
+    </row>
+    <row r="9" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>138</v>
+      </c>
+      <c r="DH9" t="s">
+        <v>25</v>
+      </c>
+      <c r="DM9">
+        <v>1.67E-3</v>
+      </c>
+      <c r="DR9">
+        <f>DM9</f>
+        <v>1.67E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>140</v>
+      </c>
+      <c r="W10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH10" t="s">
+        <v>31</v>
+      </c>
+      <c r="DI10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="DJ10" s="7"/>
+      <c r="DK10" s="7"/>
+      <c r="DL10" s="7"/>
+      <c r="DM10">
+        <v>0</v>
+      </c>
+      <c r="DR10">
+        <f>DM10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>142</v>
+      </c>
+      <c r="DH11" t="s">
+        <v>57</v>
+      </c>
+      <c r="DM11">
+        <v>2.2120000000000001E-2</v>
+      </c>
+      <c r="DR11">
+        <f>DM11</f>
+        <v>2.2120000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="W12" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR12" s="7"/>
+    </row>
+    <row r="13" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>144</v>
+      </c>
+      <c r="W13" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR13" s="7"/>
+    </row>
+    <row r="14" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>145</v>
+      </c>
+      <c r="W14" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR14" s="7"/>
+    </row>
+    <row r="15" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>146</v>
+      </c>
+      <c r="DG15" t="s">
+        <v>147</v>
+      </c>
+      <c r="DH15" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="DR15" s="12"/>
+    </row>
+    <row r="16" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>148</v>
+      </c>
+      <c r="W16" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH16" t="s">
+        <v>31</v>
+      </c>
+      <c r="DI16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DJ16" s="6"/>
+      <c r="DK16" s="6"/>
+      <c r="DL16" s="6"/>
+      <c r="DM16">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="DN16">
+        <v>0.56784000000000001</v>
+      </c>
+      <c r="DR16" s="16">
+        <f>DM16</f>
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" t="s">
+        <v>150</v>
+      </c>
+      <c r="DH17" t="s">
+        <v>4</v>
+      </c>
+      <c r="DM17">
+        <v>1.9000000000000001E-4</v>
+      </c>
+      <c r="DR17">
+        <f>DM17</f>
+        <v>1.9000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="W18" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR18" s="7"/>
+    </row>
+    <row r="19" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>152</v>
+      </c>
+      <c r="CP19" t="s">
+        <v>153</v>
+      </c>
+      <c r="DH19" t="s">
+        <v>93</v>
+      </c>
+      <c r="DM19">
+        <v>0</v>
+      </c>
+      <c r="DR19">
+        <f>DM19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>154</v>
+      </c>
+      <c r="W20" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR20" s="7"/>
+    </row>
+    <row r="21" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>155</v>
+      </c>
+      <c r="W21" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>156</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH21" t="s">
+        <v>40</v>
+      </c>
+      <c r="DI21" t="s">
+        <v>41</v>
+      </c>
+      <c r="DJ21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DK21" s="6"/>
+      <c r="DL21" s="6"/>
+      <c r="DM21">
+        <v>0</v>
+      </c>
+      <c r="DN21">
+        <v>6.2599999999999999E-3</v>
+      </c>
+      <c r="DR21">
+        <f>DM21*DN21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>157</v>
+      </c>
+      <c r="W22" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>158</v>
+      </c>
+      <c r="DH22" t="s">
+        <v>52</v>
+      </c>
+      <c r="DI22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM22">
+        <v>9.0000000000000006E-5</v>
+      </c>
+      <c r="DN22">
+        <v>0.56784000000000001</v>
+      </c>
+      <c r="DR22" s="16">
+        <f>DM22</f>
+        <v>9.0000000000000006E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="BI23" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH23" t="s">
+        <v>60</v>
+      </c>
+      <c r="DM23">
+        <v>0</v>
+      </c>
+      <c r="DR23">
+        <f>DM23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>163</v>
+      </c>
+      <c r="BW24" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH24" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="DM24">
+        <v>0</v>
+      </c>
+      <c r="DR24">
+        <f>DM24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="CD25" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH25" t="s">
+        <v>81</v>
+      </c>
+      <c r="DM25">
+        <v>1.7600000000000001E-3</v>
+      </c>
+      <c r="DR25">
+        <f>DM25</f>
+        <v>1.7600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>165</v>
+      </c>
+      <c r="W26" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR26" s="7"/>
+    </row>
+    <row r="27" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>166</v>
+      </c>
+      <c r="W27" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR27" s="7"/>
+    </row>
+    <row r="28" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>167</v>
+      </c>
+      <c r="W28" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>168</v>
+      </c>
+      <c r="DH28" t="s">
+        <v>32</v>
+      </c>
+      <c r="DI28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM28">
+        <v>0</v>
+      </c>
+      <c r="DR28">
+        <f>DM28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="W29" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR29" s="7"/>
+    </row>
+    <row r="30" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>170</v>
+      </c>
+      <c r="W30" t="s">
+        <v>113</v>
+      </c>
+      <c r="CD30" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH30" t="s">
+        <v>81</v>
+      </c>
+      <c r="DI30" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM30">
+        <v>1.7600000000000001E-3</v>
+      </c>
+      <c r="DN30">
+        <v>0.56784000000000001</v>
+      </c>
+      <c r="DR30" s="16">
+        <f>DM30</f>
+        <v>1.7600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>173</v>
+      </c>
+      <c r="W31" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR31" s="7"/>
+    </row>
+    <row r="32" spans="1:122" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="W32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CO32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CQ32" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CR32" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CS32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CU32" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="CV32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CX32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CY32" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CZ32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="DA32" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="DB32" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="DC32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="DD32" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH32" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="DR32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>176</v>
+      </c>
+      <c r="W33" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR33" s="7"/>
+    </row>
+    <row r="34" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB34" t="s">
+        <v>178</v>
+      </c>
+      <c r="DH34" t="s">
+        <v>53</v>
+      </c>
+      <c r="DM34">
+        <v>0</v>
+      </c>
+      <c r="DR34">
+        <f>DM34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>179</v>
+      </c>
+      <c r="W35" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR35" s="7"/>
+    </row>
+    <row r="36" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>180</v>
+      </c>
+      <c r="W36" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>181</v>
+      </c>
+      <c r="DH36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="DI36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM36">
+        <v>0</v>
+      </c>
+      <c r="DR36">
+        <f>DM36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>182</v>
+      </c>
+      <c r="W37" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR37" s="7"/>
+    </row>
+    <row r="38" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>183</v>
+      </c>
+      <c r="W38" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU38" t="s">
+        <v>184</v>
+      </c>
+      <c r="DH38" t="s">
+        <v>72</v>
+      </c>
+      <c r="DI38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM38">
+        <v>0</v>
+      </c>
+      <c r="DR38">
+        <f>DM38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>187</v>
+      </c>
+      <c r="W39" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR39" s="7"/>
+    </row>
+    <row r="40" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>188</v>
+      </c>
+      <c r="W40" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH40" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR40" s="7"/>
+    </row>
+    <row r="41" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>189</v>
+      </c>
+      <c r="W41" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH41" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR41" s="7"/>
+    </row>
+    <row r="42" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>116</v>
+      </c>
+      <c r="W42" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH42" t="s">
+        <v>16</v>
+      </c>
+      <c r="DI42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM42">
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="DN42">
+        <v>0.56784000000000001</v>
+      </c>
+      <c r="DR42" s="16">
+        <f>DM42</f>
+        <v>2.5999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH43" t="s">
+        <v>26</v>
+      </c>
+      <c r="DM43">
+        <v>0</v>
+      </c>
+      <c r="DR43">
+        <f>DM43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>193</v>
+      </c>
+      <c r="W44" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH44" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR44" s="7"/>
+    </row>
+    <row r="45" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>194</v>
+      </c>
+      <c r="W45" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF45" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH45" t="s">
+        <v>83</v>
+      </c>
+      <c r="DI45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM45">
+        <v>9.7E-5</v>
+      </c>
+      <c r="DN45">
+        <v>0.56784000000000001</v>
+      </c>
+      <c r="DR45" s="16">
+        <f>DM45</f>
+        <v>9.7E-5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>116</v>
+      </c>
+      <c r="R46" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="DI46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="DM46">
+        <v>2.5999999999999998E-4</v>
+      </c>
+      <c r="DN46">
+        <v>0.31802000000000002</v>
+      </c>
+      <c r="DR46">
+        <f>DM46*DN46</f>
+        <v>8.2685199999999999E-5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>196</v>
+      </c>
+      <c r="W47" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR47" s="7"/>
+    </row>
+    <row r="48" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>197</v>
+      </c>
+      <c r="W48" t="s">
+        <v>113</v>
+      </c>
+      <c r="CC48" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH48" t="s">
+        <v>80</v>
+      </c>
+      <c r="DI48" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM48">
+        <v>0</v>
+      </c>
+      <c r="DR48">
+        <f>DM48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>198</v>
+      </c>
+      <c r="W49" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR49" s="7"/>
+    </row>
+    <row r="50" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>199</v>
+      </c>
+      <c r="W50" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>168</v>
+      </c>
+      <c r="DH50" t="s">
+        <v>32</v>
+      </c>
+      <c r="DI50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM50">
+        <v>0</v>
+      </c>
+      <c r="DR50">
+        <f>DM50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>200</v>
+      </c>
+      <c r="W51" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH51" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR51" s="7"/>
+    </row>
+    <row r="52" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>202</v>
+      </c>
+      <c r="DH52" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="DR52" s="9"/>
+    </row>
+    <row r="53" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>203</v>
+      </c>
+      <c r="DG53" t="s">
+        <v>204</v>
+      </c>
+      <c r="DH53" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="DR53" s="12"/>
+    </row>
+    <row r="54" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>205</v>
+      </c>
+      <c r="CI54" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH54" t="s">
+        <v>86</v>
+      </c>
+      <c r="DM54">
+        <v>4.4000000000000002E-4</v>
+      </c>
+      <c r="DR54">
+        <f>DM54</f>
+        <v>4.4000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>206</v>
+      </c>
+      <c r="DG55" t="s">
+        <v>204</v>
+      </c>
+      <c r="DH55" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="DR55" s="12"/>
+    </row>
+    <row r="56" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>207</v>
+      </c>
+      <c r="W56" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR56" s="7"/>
+    </row>
+    <row r="57" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>208</v>
+      </c>
+      <c r="W57" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH57" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR57" s="7"/>
+    </row>
+    <row r="58" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>209</v>
+      </c>
+      <c r="DG58" t="s">
+        <v>204</v>
+      </c>
+      <c r="DH58" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="DR58" s="12"/>
+    </row>
+    <row r="59" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>210</v>
+      </c>
+      <c r="W59" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR59" s="7"/>
+    </row>
+    <row r="60" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>211</v>
+      </c>
+      <c r="W60" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR60" s="7"/>
+    </row>
+    <row r="61" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>213</v>
+      </c>
+      <c r="W61" t="s">
+        <v>113</v>
+      </c>
+      <c r="BY61" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH61" t="s">
+        <v>76</v>
+      </c>
+      <c r="DI61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM61">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="DR61" s="16">
+        <f>DM61</f>
+        <v>3.4000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>214</v>
+      </c>
+      <c r="W62" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR62" s="7"/>
+    </row>
+    <row r="63" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>215</v>
+      </c>
+      <c r="I63" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH63" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="DM63">
+        <v>0.18057999999999999</v>
+      </c>
+      <c r="DR63" s="17">
+        <f>DM63</f>
+        <v>0.18057999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>217</v>
+      </c>
+      <c r="BD64" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE64" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH64" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="DI64" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="DM64">
+        <v>1.2E-4</v>
+      </c>
+      <c r="DN64" s="3">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="DO64" s="3"/>
+      <c r="DR64">
+        <f>DM64*DN64</f>
+        <v>6.0000000000000008E-9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>218</v>
+      </c>
+      <c r="I65" t="s">
+        <v>116</v>
+      </c>
+      <c r="J65" t="s">
+        <v>115</v>
+      </c>
+      <c r="K65" t="s">
+        <v>113</v>
+      </c>
+      <c r="L65" t="s">
+        <v>114</v>
+      </c>
+      <c r="M65" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="DI65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="DJ65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="DK65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="DL65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="DM65">
+        <v>0.18057999999999999</v>
+      </c>
+      <c r="DN65">
+        <v>0.11741</v>
+      </c>
+      <c r="DO65">
+        <v>4.8000000000000001E-4</v>
+      </c>
+      <c r="DP65">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="DQ65">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="DR65">
+        <f>DM65*DN65*DO65*DP65*DQ65</f>
+        <v>1.2212293132800002E-14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:122" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="CO66" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CQ66" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CR66" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CS66" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CU66" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="CV66" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CX66" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CY66" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CZ66" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="DA66" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="DB66" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="DC66" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="DD66" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH66" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="DR66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>220</v>
+      </c>
+      <c r="W67" t="s">
+        <v>113</v>
+      </c>
+      <c r="AZ67" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH67" t="s">
+        <v>51</v>
+      </c>
+      <c r="DI67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM67">
+        <v>0</v>
+      </c>
+      <c r="DR67">
+        <f>DM67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>221</v>
+      </c>
+      <c r="W68" t="s">
+        <v>113</v>
+      </c>
+      <c r="CW68" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH68" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="DI68" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR68" s="9"/>
+    </row>
+    <row r="69" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>222</v>
+      </c>
+      <c r="BD69" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE69" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH69" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="DI69" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="DM69">
+        <v>1.2E-4</v>
+      </c>
+      <c r="DN69">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="DR69">
+        <f>DM69*DN69</f>
+        <v>6.0000000000000008E-9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>223</v>
+      </c>
+      <c r="B70" t="s">
+        <v>114</v>
+      </c>
+      <c r="W70" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH70" t="s">
+        <v>1</v>
+      </c>
+      <c r="DI70" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM70">
+        <v>0</v>
+      </c>
+      <c r="DR70">
+        <f t="shared" ref="DR70:DR75" si="0">DM70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>224</v>
+      </c>
+      <c r="K71" t="s">
+        <v>113</v>
+      </c>
+      <c r="W71" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH71" t="s">
+        <v>10</v>
+      </c>
+      <c r="DI71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM71">
+        <v>4.8000000000000001E-4</v>
+      </c>
+      <c r="DR71" s="16">
+        <f t="shared" si="0"/>
+        <v>4.8000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>225</v>
+      </c>
+      <c r="X72" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="DI72" s="1"/>
+      <c r="DM72">
+        <v>2.3000000000000001E-4</v>
+      </c>
+      <c r="DR72">
+        <f t="shared" si="0"/>
+        <v>2.3000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="DM73">
+        <v>0</v>
+      </c>
+      <c r="DR73">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH74" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="DM74">
+        <v>1.699E-6</v>
+      </c>
+      <c r="DR74">
+        <f t="shared" si="0"/>
+        <v>1.699E-6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>228</v>
+      </c>
+      <c r="AR75" t="s">
+        <v>229</v>
+      </c>
+      <c r="DH75" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="DM75">
+        <v>0</v>
+      </c>
+      <c r="DR75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX76" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH76" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="DR76" s="9"/>
+    </row>
+    <row r="77" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>231</v>
+      </c>
+      <c r="W77" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO77" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH77" t="s">
+        <v>66</v>
+      </c>
+      <c r="DI77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM77">
+        <v>0</v>
+      </c>
+      <c r="DR77">
+        <f>DM77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>232</v>
+      </c>
+      <c r="W78" t="s">
+        <v>113</v>
+      </c>
+      <c r="BZ78" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH78" t="s">
+        <v>77</v>
+      </c>
+      <c r="DI78" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM78">
+        <v>1.1E-4</v>
+      </c>
+      <c r="DR78" s="16">
+        <f>DM78</f>
+        <v>1.1E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>233</v>
+      </c>
+      <c r="CG79" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH79" t="s">
+        <v>84</v>
+      </c>
+      <c r="DM79">
+        <v>0</v>
+      </c>
+      <c r="DR79">
+        <f>DM79</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>234</v>
+      </c>
+      <c r="CM80" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH80" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="DR80" s="9"/>
+    </row>
+    <row r="81" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>235</v>
+      </c>
+      <c r="W81" t="s">
+        <v>113</v>
+      </c>
+      <c r="CN81" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH81" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="DI81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR81" s="9"/>
+    </row>
+    <row r="82" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>236</v>
+      </c>
+      <c r="H82" t="s">
+        <v>113</v>
+      </c>
+      <c r="W82" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH82" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM82">
+        <v>0</v>
+      </c>
+      <c r="DR82">
+        <f>DM82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>237</v>
+      </c>
+      <c r="W83" t="s">
+        <v>113</v>
+      </c>
+      <c r="BH83" t="s">
+        <v>229</v>
+      </c>
+      <c r="DH83" t="s">
+        <v>59</v>
+      </c>
+      <c r="DI83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM83">
+        <v>0</v>
+      </c>
+      <c r="DR83">
+        <f>DM83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>238</v>
+      </c>
+      <c r="W84" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL84" t="s">
+        <v>239</v>
+      </c>
+      <c r="DH84" t="s">
+        <v>63</v>
+      </c>
+      <c r="DI84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM84">
+        <v>0</v>
+      </c>
+      <c r="DR84">
+        <f>DM84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>240</v>
+      </c>
+      <c r="W85" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DI85" s="8"/>
+      <c r="DR85" s="7"/>
+    </row>
+    <row r="86" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>241</v>
+      </c>
+      <c r="W86" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR86" s="7"/>
+    </row>
+    <row r="87" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>242</v>
+      </c>
+      <c r="W87" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH87" t="s">
+        <v>26</v>
+      </c>
+      <c r="DI87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM87">
+        <v>0</v>
+      </c>
+      <c r="DR87">
+        <f>DM87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>243</v>
+      </c>
+      <c r="W88" t="s">
+        <v>113</v>
+      </c>
+      <c r="BV88" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH88" t="s">
+        <v>73</v>
+      </c>
+      <c r="DI88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM88">
+        <v>0</v>
+      </c>
+      <c r="DR88">
+        <f>DM88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>244</v>
+      </c>
+      <c r="CF89" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH89" t="s">
+        <v>83</v>
+      </c>
+      <c r="DM89">
+        <v>9.7E-5</v>
+      </c>
+      <c r="DR89">
+        <f>DM89</f>
+        <v>9.7E-5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>246</v>
+      </c>
+      <c r="BS90" t="s">
+        <v>115</v>
+      </c>
+      <c r="BT90" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH90" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="DI90" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="DM90">
+        <v>2.0500000000000002E-3</v>
+      </c>
+      <c r="DN90">
+        <v>5.28E-3</v>
+      </c>
+      <c r="DR90">
+        <f>DM90*DN90</f>
+        <v>1.0824E-5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>247</v>
+      </c>
+      <c r="BF91" t="s">
+        <v>142</v>
+      </c>
+      <c r="DH91" t="s">
+        <v>57</v>
+      </c>
+      <c r="DM91" s="3">
+        <v>2.2120000000000001E-2</v>
+      </c>
+      <c r="DN91" s="3"/>
+      <c r="DR91">
+        <f t="shared" ref="DR91:DR96" si="1">DM91</f>
+        <v>2.2120000000000001E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>248</v>
+      </c>
+      <c r="CJ92" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH92" t="s">
+        <v>87</v>
+      </c>
+      <c r="DM92">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="DR92">
+        <f t="shared" si="1"/>
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>249</v>
+      </c>
+      <c r="N93" t="s">
+        <v>116</v>
+      </c>
+      <c r="W93" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH93" t="s">
+        <v>13</v>
+      </c>
+      <c r="DI93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM93">
+        <v>0</v>
+      </c>
+      <c r="DR93">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>250</v>
+      </c>
+      <c r="DE94" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH94" t="s">
+        <v>108</v>
+      </c>
+      <c r="DM94">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="DR94">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>251</v>
+      </c>
+      <c r="CH95" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH95" t="s">
+        <v>85</v>
+      </c>
+      <c r="DM95">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="DR95">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>252</v>
+      </c>
+      <c r="AF96" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH96" t="s">
+        <v>31</v>
+      </c>
+      <c r="DM96">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="DR96">
+        <f t="shared" si="1"/>
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>253</v>
+      </c>
+      <c r="BF97" t="s">
+        <v>142</v>
+      </c>
+      <c r="BG97" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH97" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="DI97" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="DM97">
+        <v>2.2120000000000001E-2</v>
+      </c>
+      <c r="DN97">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="DR97">
+        <f>DM97*DN97</f>
+        <v>4.8664000000000005E-6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>254</v>
+      </c>
+      <c r="BM98" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH98" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="DI98" s="1"/>
+      <c r="DM98">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="DR98">
+        <f>DM98</f>
+        <v>4.2999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>255</v>
+      </c>
+      <c r="W99" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN99" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH99" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="DI99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM99">
+        <v>1.0499999999999999E-3</v>
+      </c>
+      <c r="DR99" s="16">
+        <f>DM99</f>
+        <v>1.0499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>256</v>
+      </c>
+      <c r="BK100" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH100" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="DR100" s="9"/>
+    </row>
+    <row r="101" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>258</v>
+      </c>
+      <c r="C101" t="s">
+        <v>229</v>
+      </c>
+      <c r="DH101" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="DR101" s="9"/>
+    </row>
+    <row r="102" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>259</v>
+      </c>
+      <c r="W102" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD102" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE102" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH102" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="DI102" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="DJ102" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DK102" s="6"/>
+      <c r="DL102" s="6"/>
+      <c r="DM102">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="DN102">
+        <v>1.7099999999999999E-3</v>
+      </c>
+      <c r="DR102" s="16">
+        <f>DM102*DN102</f>
+        <v>2.7360000000000001E-6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>260</v>
+      </c>
+      <c r="BX103" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH103" t="s">
+        <v>75</v>
+      </c>
+      <c r="DM103">
+        <v>2.0559999999999998E-2</v>
+      </c>
+      <c r="DR103">
+        <f>DM103</f>
+        <v>2.0559999999999998E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>261</v>
+      </c>
+      <c r="W104" t="s">
+        <v>113</v>
+      </c>
+      <c r="BJ104" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH104" t="s">
+        <v>61</v>
+      </c>
+      <c r="DI104" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM104">
+        <v>0</v>
+      </c>
+      <c r="DR104">
+        <f>DM104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>262</v>
+      </c>
+      <c r="AP105" t="s">
+        <v>120</v>
+      </c>
+      <c r="CA105" t="s">
+        <v>263</v>
+      </c>
+      <c r="DH105" t="s">
+        <v>41</v>
+      </c>
+      <c r="DI105" t="s">
+        <v>78</v>
+      </c>
+      <c r="DM105" s="3">
+        <v>6.2599999999999999E-3</v>
+      </c>
+      <c r="DN105">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="DR105">
+        <f>DM105*DN105</f>
+        <v>1.7527999999999998E-6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>264</v>
+      </c>
+      <c r="W106" t="s">
+        <v>113</v>
+      </c>
+      <c r="CK106" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH106" t="s">
+        <v>88</v>
+      </c>
+      <c r="DI106" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM106">
+        <v>1.2999999999999999E-4</v>
+      </c>
+      <c r="DR106" s="16">
+        <f>DM106</f>
+        <v>1.2999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>265</v>
+      </c>
+      <c r="V107" t="s">
+        <v>114</v>
+      </c>
+      <c r="W107" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH107" t="s">
+        <v>21</v>
+      </c>
+      <c r="DI107" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM107">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="DR107" s="16">
+        <f>DM107</f>
+        <v>1.4999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>266</v>
+      </c>
+      <c r="BT108" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH108" t="s">
+        <v>71</v>
+      </c>
+      <c r="DM108">
+        <v>5.28E-3</v>
+      </c>
+      <c r="DR108">
+        <f>DM108</f>
+        <v>5.28E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>267</v>
+      </c>
+      <c r="G109" t="s">
+        <v>115</v>
+      </c>
+      <c r="W109" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH109" t="s">
+        <v>6</v>
+      </c>
+      <c r="DI109" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM109">
+        <v>9.5999999999999996E-6</v>
+      </c>
+      <c r="DR109" s="16">
+        <f>DM109</f>
+        <v>9.5999999999999996E-6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>268</v>
+      </c>
+      <c r="U110" t="s">
+        <v>116</v>
+      </c>
+      <c r="W110" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH110" t="s">
+        <v>20</v>
+      </c>
+      <c r="DI110" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM110">
+        <v>0</v>
+      </c>
+      <c r="DR110">
+        <f>DM110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>269</v>
+      </c>
+      <c r="AK111" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL111" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH111" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="DI111" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="DJ111" s="4"/>
+      <c r="DK111" s="4"/>
+      <c r="DL111" s="4"/>
+      <c r="DM111">
+        <v>0</v>
+      </c>
+      <c r="DN111">
+        <v>0</v>
+      </c>
+      <c r="DR111">
+        <f>DM111*DN111</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>270</v>
+      </c>
+      <c r="AW112" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH112" t="s">
+        <v>48</v>
+      </c>
+      <c r="DM112">
+        <v>8.4000000000000003E-4</v>
+      </c>
+      <c r="DR112">
+        <f>DM112</f>
+        <v>8.4000000000000003E-4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>271</v>
+      </c>
+      <c r="W113" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG113" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH113" t="s">
+        <v>58</v>
+      </c>
+      <c r="DI113" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM113">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="DR113" s="16">
+        <f>DM113</f>
+        <v>2.2000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>272</v>
+      </c>
+      <c r="W114" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ114" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH114" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="DI114" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM114" s="11">
+        <v>8.484E-7</v>
+      </c>
+      <c r="DR114" s="18">
+        <f>DM114</f>
+        <v>8.484E-7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>273</v>
+      </c>
+      <c r="BR115" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH115" t="s">
+        <v>69</v>
+      </c>
+      <c r="DM115">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="DR115">
+        <f>DM115</f>
+        <v>2.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>274</v>
+      </c>
+      <c r="W116" t="s">
+        <v>113</v>
+      </c>
+      <c r="CE116" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH116" t="s">
+        <v>82</v>
+      </c>
+      <c r="DI116" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM116">
+        <v>1E-4</v>
+      </c>
+      <c r="DR116" s="16">
+        <f>DM116</f>
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>275</v>
+      </c>
+      <c r="W117" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH117" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR117" s="7"/>
+    </row>
+    <row r="118" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>276</v>
+      </c>
+      <c r="DF118" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH118" t="s">
+        <v>109</v>
+      </c>
+      <c r="DM118">
+        <v>0</v>
+      </c>
+      <c r="DR118">
+        <f>DM118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>277</v>
+      </c>
+      <c r="W119" t="s">
+        <v>113</v>
+      </c>
+      <c r="CT119" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH119" t="s">
+        <v>97</v>
+      </c>
+      <c r="DI119" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM119">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="DR119" s="16">
+        <f>DM119</f>
+        <v>1.6000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>279</v>
+      </c>
+      <c r="AV120" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH120" t="s">
+        <v>47</v>
+      </c>
+      <c r="DM120">
+        <v>0</v>
+      </c>
+      <c r="DR120">
+        <f>DM120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:122" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="W121" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CD121" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="CO121" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CQ121" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CR121" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CS121" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CU121" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="CV121" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CX121" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="CY121" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CZ121" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="DA121" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="DB121" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="DC121" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="DD121" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH121" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="DR121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>281</v>
+      </c>
+      <c r="W122" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH122" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR122" s="7"/>
+    </row>
+    <row r="123" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>282</v>
+      </c>
+      <c r="S123" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH123" t="s">
+        <v>18</v>
+      </c>
+      <c r="DM123">
+        <v>0</v>
+      </c>
+      <c r="DR123">
+        <f>DM123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>283</v>
+      </c>
+      <c r="AS124" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH124" t="s">
+        <v>44</v>
+      </c>
+      <c r="DM124">
+        <v>0</v>
+      </c>
+      <c r="DR124">
+        <f>DM124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>284</v>
+      </c>
+      <c r="AG125" t="s">
+        <v>168</v>
+      </c>
+      <c r="DH125" t="s">
+        <v>32</v>
+      </c>
+      <c r="DM125">
+        <v>0</v>
+      </c>
+      <c r="DR125">
+        <f>DM125</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>285</v>
+      </c>
+      <c r="W126" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH126" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DI126" s="10"/>
+      <c r="DR126" s="7"/>
+    </row>
+    <row r="127" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>286</v>
+      </c>
+      <c r="W127" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG127" t="s">
+        <v>168</v>
+      </c>
+      <c r="DH127" t="s">
+        <v>32</v>
+      </c>
+      <c r="DI127" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM127">
+        <v>0</v>
+      </c>
+      <c r="DR127">
+        <f>DM127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>287</v>
+      </c>
+      <c r="W128" t="s">
+        <v>113</v>
+      </c>
+      <c r="CD128" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH128" t="s">
+        <v>81</v>
+      </c>
+      <c r="DI128" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM128">
+        <v>1.7600000000000001E-3</v>
+      </c>
+      <c r="DR128" s="16">
+        <f>DM128</f>
+        <v>1.7600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>288</v>
+      </c>
+      <c r="W129" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH129" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR129" s="7"/>
+    </row>
+    <row r="130" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>289</v>
+      </c>
+      <c r="W130" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN130" t="s">
+        <v>156</v>
+      </c>
+      <c r="AP130" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH130" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="DI130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="DJ130" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DK130" s="6"/>
+      <c r="DL130" s="6"/>
+      <c r="DM130">
+        <v>4.9100000000000003E-3</v>
+      </c>
+      <c r="DN130">
+        <v>6.2599999999999999E-3</v>
+      </c>
+      <c r="DR130">
+        <f>DM130*DN130</f>
+        <v>3.07366E-5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI131" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH131" t="s">
+        <v>34</v>
+      </c>
+      <c r="DM131">
+        <v>0</v>
+      </c>
+      <c r="DR131">
+        <f>DM131</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>291</v>
+      </c>
+      <c r="AT132" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH132" t="s">
+        <v>45</v>
+      </c>
+      <c r="DM132">
+        <v>0</v>
+      </c>
+      <c r="DR132">
+        <f>DM132</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ133" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH133" t="s">
+        <v>42</v>
+      </c>
+      <c r="DM133">
+        <v>0</v>
+      </c>
+      <c r="DR133">
+        <f>DM133</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>293</v>
+      </c>
+      <c r="W134" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH134" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DI134" s="8"/>
+      <c r="DR134" s="7"/>
+    </row>
+    <row r="135" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>294</v>
+      </c>
+      <c r="W135" t="s">
+        <v>113</v>
+      </c>
+      <c r="CL135" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH135" t="s">
+        <v>89</v>
+      </c>
+      <c r="DI135" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM135">
+        <v>0</v>
+      </c>
+      <c r="DR135">
+        <f>DM135</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>295</v>
+      </c>
+      <c r="F136" t="s">
+        <v>114</v>
+      </c>
+      <c r="W136" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH136" t="s">
+        <v>5</v>
+      </c>
+      <c r="DI136" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM136">
+        <v>0</v>
+      </c>
+      <c r="DR136">
+        <f>DM136</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>296</v>
+      </c>
+      <c r="W137" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC137" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH137" t="s">
+        <v>28</v>
+      </c>
+      <c r="DI137" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM137">
+        <v>0</v>
+      </c>
+      <c r="DR137">
+        <f>DM137</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>297</v>
+      </c>
+      <c r="W138" t="s">
+        <v>113</v>
+      </c>
+      <c r="BP138" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH138" t="s">
+        <v>67</v>
+      </c>
+      <c r="DI138" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM138">
+        <v>0</v>
+      </c>
+      <c r="DR138">
+        <f>DM138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>298</v>
+      </c>
+      <c r="D139" t="s">
+        <v>114</v>
+      </c>
+      <c r="W139" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH139" t="s">
+        <v>3</v>
+      </c>
+      <c r="DI139" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM139">
+        <v>0</v>
+      </c>
+      <c r="DR139">
+        <f>DM139</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>299</v>
+      </c>
+      <c r="I140" t="s">
+        <v>116</v>
+      </c>
+      <c r="J140" t="s">
+        <v>115</v>
+      </c>
+      <c r="W140" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH140" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="DI140" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="DJ140" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DK140" s="6"/>
+      <c r="DL140" s="6"/>
+      <c r="DM140">
+        <v>0.18057999999999999</v>
+      </c>
+      <c r="DN140">
+        <v>0.11741</v>
+      </c>
+      <c r="DR140" s="17">
+        <f>DN140*DM140</f>
+        <v>2.1201897799999998E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>300</v>
+      </c>
+      <c r="W141" t="s">
+        <v>113</v>
+      </c>
+      <c r="BC141" t="s">
+        <v>150</v>
+      </c>
+      <c r="DH141" t="s">
+        <v>54</v>
+      </c>
+      <c r="DI141" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM141">
+        <v>0</v>
+      </c>
+      <c r="DR141">
+        <f>DM141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>301</v>
+      </c>
+      <c r="W142" t="s">
+        <v>113</v>
+      </c>
+      <c r="CD142" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH142" t="s">
+        <v>81</v>
+      </c>
+      <c r="DI142" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM142">
+        <v>1.7600000000000001E-3</v>
+      </c>
+      <c r="DR142" s="16">
+        <f>DM142</f>
+        <v>1.7600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>302</v>
+      </c>
+      <c r="T143" t="s">
+        <v>113</v>
+      </c>
+      <c r="W143" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH143" t="s">
+        <v>19</v>
+      </c>
+      <c r="DI143" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DR143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>303</v>
+      </c>
+      <c r="W144" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH144" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DI144" s="8"/>
+      <c r="DR144" s="7"/>
+    </row>
+    <row r="145" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>304</v>
+      </c>
+      <c r="W145" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH145" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH145" t="s">
+        <v>33</v>
+      </c>
+      <c r="DI145" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM145">
+        <v>0</v>
+      </c>
+      <c r="DR145">
+        <f>DM145</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>305</v>
+      </c>
+      <c r="W146" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU146" t="s">
+        <v>306</v>
+      </c>
+      <c r="DH146" t="s">
+        <v>46</v>
+      </c>
+      <c r="DI146" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM146">
+        <v>0</v>
+      </c>
+      <c r="DR146">
+        <f>DM146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>307</v>
+      </c>
+      <c r="P147" t="s">
+        <v>115</v>
+      </c>
+      <c r="DH147" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="DR147" s="9"/>
+    </row>
+    <row r="148" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>308</v>
+      </c>
+      <c r="AM148" t="s">
+        <v>116</v>
+      </c>
+      <c r="DH148" t="s">
+        <v>38</v>
+      </c>
+      <c r="DM148">
+        <v>0</v>
+      </c>
+      <c r="DR148">
+        <f>DM148</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>309</v>
+      </c>
+      <c r="CB149" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH149" t="s">
+        <v>79</v>
+      </c>
+      <c r="DM149">
+        <v>0</v>
+      </c>
+      <c r="DR149">
+        <f>DM149</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>311</v>
+      </c>
+      <c r="W150" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH150" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DI150" s="10"/>
+      <c r="DR150" s="7"/>
+    </row>
+    <row r="151" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>312</v>
+      </c>
+      <c r="O151" t="s">
+        <v>113</v>
+      </c>
+      <c r="W151" t="s">
+        <v>113</v>
+      </c>
+      <c r="DH151" t="s">
+        <v>14</v>
+      </c>
+      <c r="DI151" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="DM151">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="DR151" s="16">
+        <f>DM151</f>
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:122" x14ac:dyDescent="0.25">
+      <c r="DR152">
+        <f>(SUM(DR6:DR151))*100</f>
+        <v>30.004165820001223</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>